--- a/data/sources/countries/cuba.xlsx
+++ b/data/sources/countries/cuba.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,298 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI5"/>
+  <dimension ref="A1:BF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source3</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>PROVINCE</t>
         </is>
       </c>
     </row>
@@ -824,7 +733,7 @@
           <t>CUB</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>192</t>
         </is>
@@ -839,7 +748,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Shanghai Electric</t>
+          <t>SE Energy Investment Co.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -899,22 +808,27 @@
       <c r="BA2" t="n">
         <v>5</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BB2" t="n">
         <v>0</v>
       </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>https://www.pv-tech.org/hive-and-shanghai-electric-to-build-50mw-of-solar-in-cuba/</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>https://www.power-technology.com/data-insights/power-plant-profile-mariel-free-zone-solar-pv-park-cuba/</t>
+        </is>
+      </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>https://www.pv-tech.org/hive-and-shanghai-electric-to-build-50mw-of-solar-in-cuba/</t>
+          <t>https://havana-live.com/uk-and-chinese-company-to-build-50mw-of-solar-in-mariel/</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>https://www.power-technology.com/data-insights/power-plant-profile-mariel-free-zone-solar-pv-park-cuba/</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>https://havana-live.com/uk-and-chinese-company-to-build-50mw-of-solar-in-mariel/</t>
+          <t>ARTEMISA</t>
         </is>
       </c>
     </row>
@@ -942,7 +856,7 @@
           <t>CUB</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>192</t>
         </is>
@@ -1011,22 +925,27 @@
       <c r="BA3" t="n">
         <v>5</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BB3" t="n">
         <v>0</v>
       </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>https://eltoque.com/es/que-sabemos-del-plan-de-55-parques-solares-fotovoltaicos-que-prometio-el-gobierno-cubano</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>https://havanatimesenespanol.org/reportajes/los-55-parques-solares-que-planea-el-gobierno-cubano/</t>
+        </is>
+      </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>https://eltoque.com/es/que-sabemos-del-plan-de-55-parques-solares-fotovoltaicos-que-prometio-el-gobierno-cubano</t>
+          <t>https://www.pv-magazine-latam.com/2025/10/21/cuba-ya-tiene-32-parques-fotovoltaicos-en-operacion-de-los-55-previstos-para-este-ano/</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>https://havanatimesenespanol.org/reportajes/los-55-parques-solares-que-planea-el-gobierno-cubano/</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>https://www.pv-magazine-latam.com/2025/10/21/cuba-ya-tiene-32-parques-fotovoltaicos-en-operacion-de-los-55-previstos-para-este-ano/</t>
+          <t>CIENFUEGOS</t>
         </is>
       </c>
     </row>
@@ -1054,7 +973,7 @@
           <t>CUB</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>192</t>
         </is>
@@ -1069,7 +988,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Government of China</t>
+          <t>Gobierno de la Republica Popular China</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1126,32 +1045,37 @@
       <c r="BA4" t="n">
         <v>3</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BB4" t="n">
         <v>0</v>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>https://dialogo-americas.com/articles/chinas-solar-energy-projects-deepen-cubas-technological-dependence/</t>
         </is>
       </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>https://prensamercosur.org/2026/07/28/energia-solar-china-profundiza-la-dependencia-tecnologica-de-cuba/</t>
+        </is>
+      </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>https://prensamercosur.org/2026/07/28/energia-solar-china-profundiza-la-dependencia-tecnologica-de-cuba/</t>
+          <t>CIUDAD DE LA HABANA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CUB-0005</t>
+          <t>CUB-0004</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22.9297, -82.6889</t>
+          <t>23.113592, -82.366592</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1164,22 +1088,22 @@
           <t>CUB</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CU-15</t>
+          <t>CU-03</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2016</v>
+        <v>2000</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Yutong</t>
+          <t>Huawei Technologies</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1192,32 +1116,35 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>ICT</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Manufactura</t>
+          <t>TIC</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Ensamblaje local de omnibus Yutong</t>
+          <t>Contrato para construir la red nacional de fibra optica de Cuba, base de la posterior modernizacion de las telecomunicaciones. El Gobierno chino desembolso USD 200M en mayo de 2000 para financiar esa modernizacion. Huawei sigue siendo el principal proveedor de ETECSA y participa en la transicion de la television analogica a la digital y en la ampliacion de la banda ancha movil.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Local assembly of Yutong buses</t>
+          <t>Contract to build Cuba's national fibre optic network</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ARTEMISA</t>
-        </is>
+          <t>LA HABANA, CUBA</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>200</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Adquisición</t>
+          <t>Construcción</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1233,22 +1160,144 @@
       <c r="BA5" t="n">
         <v>3</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BB5" t="n">
         <v>0</v>
       </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>https://www.martinoticias.com/a/huawei-cuba-telefonos-infraestrctura-censura/152008.html</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>https://www.yucabyte.org/2022/02/16/etecsa-infraestructura/</t>
+        </is>
+      </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>https://www.connectas.org/especiales/telecomunicaciones-cuba/</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>CIUDAD DE LA HABANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CUB-0005</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>22.9297, -82.6889</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CUB</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CU-15</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Zhengzhou Yutong Bus Co.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Punto</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Manufactura</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Ensamblaje local de omnibus Yutong</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Local assembly of Yutong buses</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ARTEMISA</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Adquisición</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
           <t>https://www.cibercuba.com/noticias/2016-06-29-u129488-la-yutong-y-la-empresa-cubana-estatal-caisa-montaran-650-autobuses-en</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>http://www.cubadebate.cu/noticias/2018/06/20/omnibus-yutong-nuevos-contratos-y-convenios-en-cuba-fotos/</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>https://www.martinoticias.com/a/yutong-cuba-ensambladora-autobuses-/37949.html</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>ARTEMISA</t>
         </is>
       </c>
     </row>

--- a/data/sources/countries/cuba.xlsx
+++ b/data/sources/countries/cuba.xlsx
@@ -46,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF6"/>
+  <dimension ref="A1:BH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,25 +684,35 @@
       </c>
       <c r="BB1" t="inlineStr">
         <is>
+          <t>reliability_notes</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>cancelled_motivo</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>source3</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>PROVINCE</t>
         </is>
@@ -715,6 +724,7 @@
           <t>CUB-0001</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1</v>
       </c>
@@ -733,10 +743,8 @@
           <t>CUB</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="G2" t="n">
+        <v>192</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -787,6 +795,8 @@
       <c r="R2" t="n">
         <v>60</v>
       </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
         <v>50</v>
       </c>
@@ -805,28 +815,58 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
         <v>5</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
         <v>0</v>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>https://www.pv-tech.org/hive-and-shanghai-electric-to-build-50mw-of-solar-in-cuba/</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>https://www.power-technology.com/data-insights/power-plant-profile-mariel-free-zone-solar-pv-park-cuba/</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>https://havana-live.com/uk-and-chinese-company-to-build-50mw-of-solar-in-mariel/</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>ARTEMISA</t>
         </is>
@@ -838,6 +878,7 @@
           <t>CUB-0002</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>2</v>
       </c>
@@ -856,10 +897,8 @@
           <t>CUB</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="G3" t="n">
+        <v>192</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -907,6 +946,10 @@
           <t>CIENFUEGOS, CUBA</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -922,28 +965,58 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
         <v>5</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
         <v>0</v>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr">
         <is>
           <t>https://eltoque.com/es/que-sabemos-del-plan-de-55-parques-solares-fotovoltaicos-que-prometio-el-gobierno-cubano</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>https://havanatimesenespanol.org/reportajes/los-55-parques-solares-que-planea-el-gobierno-cubano/</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>https://www.pv-magazine-latam.com/2025/10/21/cuba-ya-tiene-32-parques-fotovoltaicos-en-operacion-de-los-55-previstos-para-este-ano/</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>CIENFUEGOS</t>
         </is>
@@ -955,6 +1028,7 @@
           <t>CUB-0003</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>3</v>
       </c>
@@ -973,10 +1047,8 @@
           <t>CUB</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="G4" t="n">
+        <v>192</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1027,6 +1099,9 @@
       <c r="R4" t="n">
         <v>80</v>
       </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1042,23 +1117,54 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
         <v>3</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
         <v>0</v>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr">
         <is>
           <t>https://dialogo-americas.com/articles/chinas-solar-energy-projects-deepen-cubas-technological-dependence/</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>https://prensamercosur.org/2026/07/28/energia-solar-china-profundiza-la-dependencia-tecnologica-de-cuba/</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr">
         <is>
           <t>CIUDAD DE LA HABANA</t>
         </is>
@@ -1067,15 +1173,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CUB-0004</t>
-        </is>
-      </c>
+          <t>CUB-0005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23.113592, -82.366592</t>
+          <t>22.9297, -82.6889</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1088,22 +1195,20 @@
           <t>CUB</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="G5" t="n">
+        <v>192</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CU-03</t>
+          <t>CU-15</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2000</v>
+        <v>2016</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Huawei Technologies</t>
+          <t>Zhengzhou Yutong Bus Co.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1116,35 +1221,36 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ICT</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>TIC</t>
+          <t>Manufactura</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Contrato para construir la red nacional de fibra optica de Cuba, base de la posterior modernizacion de las telecomunicaciones. El Gobierno chino desembolso USD 200M en mayo de 2000 para financiar esa modernizacion. Huawei sigue siendo el principal proveedor de ETECSA y participa en la transicion de la television analogica a la digital y en la ampliacion de la banda ancha movil.</t>
+          <t>Ensamblaje local de omnibus Yutong</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Contract to build Cuba's national fibre optic network</t>
+          <t>Local assembly of Yutong buses</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>LA HABANA, CUBA</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>200</v>
-      </c>
+          <t>ARTEMISA</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Construcción</t>
+          <t>Adquisición</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1157,145 +1263,58 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
         <v>3</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
         <v>0</v>
       </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>https://www.martinoticias.com/a/huawei-cuba-telefonos-infraestrctura-censura/152008.html</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>https://www.yucabyte.org/2022/02/16/etecsa-infraestructura/</t>
-        </is>
-      </c>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>https://www.connectas.org/especiales/telecomunicaciones-cuba/</t>
+          <t>https://www.cibercuba.com/noticias/2016-06-29-u129488-la-yutong-y-la-empresa-cubana-estatal-caisa-montaran-650-autobuses-en</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA HABANA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CUB-0005</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>22.9297, -82.6889</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Cuba</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CUB</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CU-15</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2016</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Zhengzhou Yutong Bus Co.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Manufacturing</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Manufactura</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Ensamblaje local de omnibus Yutong</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Local assembly of Yutong buses</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>ARTEMISA</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Adquisición</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BA6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>https://www.cibercuba.com/noticias/2016-06-29-u129488-la-yutong-y-la-empresa-cubana-estatal-caisa-montaran-650-autobuses-en</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
           <t>http://www.cubadebate.cu/noticias/2018/06/20/omnibus-yutong-nuevos-contratos-y-convenios-en-cuba-fotos/</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>https://www.martinoticias.com/a/yutong-cuba-ensambladora-autobuses-/37949.html</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>ARTEMISA</t>
         </is>

--- a/data/sources/countries/cuba.xlsx
+++ b/data/sources/countries/cuba.xlsx
@@ -933,7 +933,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Programa nacional de parques solares fotovoltaicos octubre de 2025 y 49 conectados entre inicios de 2025 e inicios de 2026, sumando mas de 1.000 MW. El compromiso del embajador chino es de 92 parques y unos 2.000 MW para 2028.</t>
+          <t>Programa nacional de parques solares fotovoltaicos octubre de 2025 y 49 conectados entre inicios de 2025 e inicios de.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
